--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127295629</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127295629</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127295629</v>
+        <v>127424694</v>
       </c>
       <c r="B2" t="n">
         <v>98443</v>
@@ -705,12 +705,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 3 Gagnef Rista 2:11 (2), Knärot 3 Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500585</v>
+        <v>500532</v>
       </c>
       <c r="R2" t="n">
-        <v>6698773</v>
+        <v>6698798</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,6 +793,718 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127424517</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Knärot 1 Gagnef Rista 2:11 (2), Knärot 1 Gagnef Rista 2:11 (2), Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>500541</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6698773</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127424978</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Knärot 6 Gagnef Rista 2:11 (2), Knärot 5 Gagnef Rista 2:11 (2), Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>500490</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6698826</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127425587</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Knärot 6 Gagnef Rista 2:11 (2), Järpe Gagnef Rista 2:11 (2), Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>500442</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6698687</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127425712</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gagnef Rista 2:11 (2), Gagnef Rista 2:11 (2), Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>500571</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6698739</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127424556</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Knärot 2 Gagnef Rista 2:11 (2), Knärot 2 Gagnef Rista 2:11 (2), Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>500527</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6698769</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127425365</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Knärot 6 Gagnef Rista 2:11 (2), Järpe Gagnef Rista 2:11 (2), Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>500442</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6698687</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127424694</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>127424517</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>127424978</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>127425587</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>127425712</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127424556</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>127425365</v>
       </c>
       <c r="B8" t="n">
-        <v>56840</v>
+        <v>56844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127424694</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>127424517</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>127424978</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>127425587</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>127425712</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127424556</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127424694</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>127424517</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>127424978</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>127425587</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>127425712</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127424556</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>127425365</v>
       </c>
       <c r="B8" t="n">
-        <v>56844</v>
+        <v>56846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127424694</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>127424517</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>127424978</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>127425587</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>127425712</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127424556</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127424694</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>127424517</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>127424978</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>127425587</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>127425712</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127424556</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>127425365</v>
       </c>
       <c r="B8" t="n">
-        <v>56846</v>
+        <v>56849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127424694</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>127424517</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>127424978</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>127425587</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>127425712</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127424556</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>127425365</v>
       </c>
       <c r="B8" t="n">
-        <v>56849</v>
+        <v>56855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127424694</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>127424517</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>127424978</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>127425587</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>127425712</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127424556</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127424694</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>127424517</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>127424978</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>127425587</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>127425712</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127424556</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127424694</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>127424517</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>127424978</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>127425587</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>127425712</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>127424556</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127424694</v>
+        <v>127295629</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,12 +705,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knärot 3 Gagnef Rista 2:11 (2), Knärot 3 Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500532</v>
+        <v>500585</v>
       </c>
       <c r="R2" t="n">
-        <v>6698798</v>
+        <v>6698773</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127424517</v>
+        <v>127424694</v>
       </c>
       <c r="B3" t="n">
         <v>98470</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -841,14 +841,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knärot 1 Gagnef Rista 2:11 (2), Knärot 1 Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 3 Gagnef Rista 2:11 (2), Knärot 3 Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500541</v>
+        <v>500532</v>
       </c>
       <c r="R3" t="n">
-        <v>6698773</v>
+        <v>6698798</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127424978</v>
+        <v>127424517</v>
       </c>
       <c r="B4" t="n">
         <v>98470</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,17 +962,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knärot 6 Gagnef Rista 2:11 (2), Knärot 5 Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 1 Gagnef Rista 2:11 (2), Knärot 1 Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500490</v>
+        <v>500541</v>
       </c>
       <c r="R4" t="n">
-        <v>6698826</v>
+        <v>6698773</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127425587</v>
+        <v>127424978</v>
       </c>
       <c r="B5" t="n">
         <v>98470</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knärot 6 Gagnef Rista 2:11 (2), Järpe Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 6 Gagnef Rista 2:11 (2), Knärot 5 Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500442</v>
+        <v>500490</v>
       </c>
       <c r="R5" t="n">
-        <v>6698687</v>
+        <v>6698826</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127425712</v>
+        <v>127425587</v>
       </c>
       <c r="B6" t="n">
         <v>98470</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1204,17 +1204,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gagnef Rista 2:11 (2), Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 6 Gagnef Rista 2:11 (2), Järpe Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500571</v>
+        <v>500442</v>
       </c>
       <c r="R6" t="n">
-        <v>6698739</v>
+        <v>6698687</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127424556</v>
+        <v>127425712</v>
       </c>
       <c r="B7" t="n">
         <v>98470</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Knärot 2 Gagnef Rista 2:11 (2), Knärot 2 Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Gagnef Rista 2:11 (2), Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500527</v>
+        <v>500571</v>
       </c>
       <c r="R7" t="n">
-        <v>6698769</v>
+        <v>6698739</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,48 +1401,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127425365</v>
+        <v>127424556</v>
       </c>
       <c r="B8" t="n">
-        <v>56855</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Knärot 6 Gagnef Rista 2:11 (2), Järpe Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 2 Gagnef Rista 2:11 (2), Knärot 2 Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500442</v>
+        <v>500527</v>
       </c>
       <c r="R8" t="n">
-        <v>6698687</v>
+        <v>6698769</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,22 +1480,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,6 +1519,113 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127425365</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Knärot 6 Gagnef Rista 2:11 (2), Järpe Gagnef Rista 2:11 (2), Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>500442</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6698687</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127295629</v>
+        <v>127424694</v>
       </c>
       <c r="B2" t="n">
-        <v>98436</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,12 +705,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 3 Gagnef Rista 2:11 (2), Knärot 3 Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500585</v>
+        <v>500532</v>
       </c>
       <c r="R2" t="n">
-        <v>6698773</v>
+        <v>6698798</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127424694</v>
+        <v>127424517</v>
       </c>
       <c r="B3" t="n">
         <v>98470</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -841,14 +841,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knärot 3 Gagnef Rista 2:11 (2), Knärot 3 Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 1 Gagnef Rista 2:11 (2), Knärot 1 Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500532</v>
+        <v>500541</v>
       </c>
       <c r="R3" t="n">
-        <v>6698798</v>
+        <v>6698773</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127424517</v>
+        <v>127424978</v>
       </c>
       <c r="B4" t="n">
         <v>98470</v>
@@ -947,7 +947,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,17 +962,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knärot 1 Gagnef Rista 2:11 (2), Knärot 1 Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 6 Gagnef Rista 2:11 (2), Knärot 5 Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500541</v>
+        <v>500490</v>
       </c>
       <c r="R4" t="n">
-        <v>6698773</v>
+        <v>6698826</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127424978</v>
+        <v>127425587</v>
       </c>
       <c r="B5" t="n">
         <v>98470</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knärot 6 Gagnef Rista 2:11 (2), Knärot 5 Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 6 Gagnef Rista 2:11 (2), Järpe Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500490</v>
+        <v>500442</v>
       </c>
       <c r="R5" t="n">
-        <v>6698826</v>
+        <v>6698687</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,7 +1159,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127425587</v>
+        <v>127425712</v>
       </c>
       <c r="B6" t="n">
         <v>98470</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1204,17 +1204,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knärot 6 Gagnef Rista 2:11 (2), Järpe Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Gagnef Rista 2:11 (2), Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500442</v>
+        <v>500571</v>
       </c>
       <c r="R6" t="n">
-        <v>6698687</v>
+        <v>6698739</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127425712</v>
+        <v>127424556</v>
       </c>
       <c r="B7" t="n">
         <v>98470</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>122</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gagnef Rista 2:11 (2), Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 2 Gagnef Rista 2:11 (2), Knärot 2 Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500571</v>
+        <v>500527</v>
       </c>
       <c r="R7" t="n">
-        <v>6698739</v>
+        <v>6698769</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,62 +1401,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127424556</v>
+        <v>127425365</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>56855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Knärot 2 Gagnef Rista 2:11 (2), Knärot 2 Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 6 Gagnef Rista 2:11 (2), Järpe Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>500527</v>
+        <v>500442</v>
       </c>
       <c r="R8" t="n">
-        <v>6698769</v>
+        <v>6698687</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1480,22 +1466,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,113 +1505,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>127425365</v>
-      </c>
-      <c r="B9" t="n">
-        <v>56855</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Knärot 6 Gagnef Rista 2:11 (2), Järpe Gagnef Rista 2:11 (2), Dlr</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>500442</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6698687</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Gagnef</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Gagnef</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127424694</v>
+        <v>127425365</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>57132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Knärot 3 Gagnef Rista 2:11 (2), Knärot 3 Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 6 Gagnef Rista 2:11 (2), Järpe Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500532</v>
+        <v>500442</v>
       </c>
       <c r="R2" t="n">
-        <v>6698798</v>
+        <v>6698687</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +785,7 @@
         <v>127424517</v>
       </c>
       <c r="B3" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127424978</v>
+        <v>127424556</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>122</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,17 +948,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knärot 6 Gagnef Rista 2:11 (2), Knärot 5 Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 2 Gagnef Rista 2:11 (2), Knärot 2 Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>500490</v>
+        <v>500527</v>
       </c>
       <c r="R4" t="n">
-        <v>6698826</v>
+        <v>6698769</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127425587</v>
+        <v>127424617</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1083,17 +1069,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knärot 6 Gagnef Rista 2:11 (2), Järpe Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Gagnef Rista 2:11 (2), Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>500442</v>
+        <v>500551</v>
       </c>
       <c r="R5" t="n">
-        <v>6698687</v>
+        <v>6698811</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1132,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127425712</v>
+        <v>127424694</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,12 +1175,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1204,17 +1190,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gagnef Rista 2:11 (2), Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 3 Gagnef Rista 2:11 (2), Knärot 3 Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>500571</v>
+        <v>500532</v>
       </c>
       <c r="R6" t="n">
-        <v>6698739</v>
+        <v>6698798</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1243,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127424556</v>
+        <v>127424908</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,12 +1296,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1325,17 +1306,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Knärot 2 Gagnef Rista 2:11 (2), Knärot 2 Gagnef Rista 2:11 (2), Dlr</t>
+          <t>Knärot 6 Gagnef Rista 2:11 (2), Knärot 5 Gagnef Rista 2:11 (2), Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>500527</v>
+        <v>500490</v>
       </c>
       <c r="R7" t="n">
-        <v>6698769</v>
+        <v>6698826</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1374,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,35 +1382,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127425365</v>
+        <v>127425587</v>
       </c>
       <c r="B8" t="n">
-        <v>56855</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Knärot 6 Gagnef Rista 2:11 (2), Järpe Gagnef Rista 2:11 (2), Dlr</t>
@@ -1466,22 +1461,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,6 +1500,127 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127425712</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gagnef Rista 2:11 (2), Gagnef Rista 2:11 (2), Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>500571</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6698739</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35464-2025 artfynd.xlsx
+++ b/artfynd/A 35464-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127425365</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127424517</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127424556</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1142,6 +1162,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127424617</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127424694</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1379,6 +1409,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127424908</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127425587</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1621,8 +1661,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127425712</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>